--- a/d/2026-07-23_会员有效性分析.xlsx
+++ b/d/2026-07-23_会员有效性分析.xlsx
@@ -6268,7 +6268,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6291,7 +6291,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6314,7 +6314,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13161289910</t>
+          <t>131****9910</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6337,7 +6337,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13293019486</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6360,7 +6360,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13171607183</t>
+          <t>131****7183</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6383,7 +6383,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15701060983</t>
+          <t>157****0983</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6406,7 +6406,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13879686023</t>
+          <t>138****6023</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6429,7 +6429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17732888060</t>
+          <t>177****8060</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6452,7 +6452,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15378954286</t>
+          <t>153****4286</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6475,7 +6475,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13911246265</t>
+          <t>139****6265</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6498,7 +6498,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15201123395</t>
+          <t>152****3395</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6521,7 +6521,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18511946513</t>
+          <t>185****6513</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6544,7 +6544,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13272824691</t>
+          <t>132****4691</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6567,7 +6567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6590,7 +6590,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18511226888</t>
+          <t>185****6888</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6613,7 +6613,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17278102448</t>
+          <t>172****2448</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6636,7 +6636,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13237413419</t>
+          <t>132****3419</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6659,7 +6659,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19814911319</t>
+          <t>198****1319</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6682,7 +6682,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15663258696</t>
+          <t>156****8696</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6705,7 +6705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13521234380</t>
+          <t>135****4380</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6728,7 +6728,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18219829757</t>
+          <t>182****9757</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6751,7 +6751,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18611722515</t>
+          <t>186****2515</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6774,7 +6774,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17621765589</t>
+          <t>176****5589</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6797,7 +6797,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15311196683</t>
+          <t>153****6683</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6820,7 +6820,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18210182706</t>
+          <t>182****2706</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6843,7 +6843,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15891781131</t>
+          <t>158****1131</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6866,7 +6866,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13811162976</t>
+          <t>138****2976</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6889,7 +6889,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>18811031085</t>
+          <t>188****1085</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6912,7 +6912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15227416428</t>
+          <t>152****6428</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6935,7 +6935,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>18610932185</t>
+          <t>186****2185</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6958,7 +6958,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13911290670</t>
+          <t>139****0670</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6981,7 +6981,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13717797690</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7004,7 +7004,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17368461289</t>
+          <t>173****1289</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7027,7 +7027,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -7050,7 +7050,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17883180691</t>
+          <t>178****0691</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7073,7 +7073,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15521301582</t>
+          <t>155****1582</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7096,7 +7096,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13521788196</t>
+          <t>135****8196</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7119,7 +7119,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15733359639</t>
+          <t>157****9639</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7142,7 +7142,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17601663766</t>
+          <t>176****3766</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7165,7 +7165,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18245704734</t>
+          <t>182****4734</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7188,7 +7188,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15330073070</t>
+          <t>153****3070</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7211,7 +7211,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7234,7 +7234,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15397387154</t>
+          <t>153****7154</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7257,7 +7257,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13269815521</t>
+          <t>132****5521</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7280,7 +7280,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18930090939</t>
+          <t>189****0939</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7303,7 +7303,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15811504668</t>
+          <t>158****4668</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7326,7 +7326,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13520701786</t>
+          <t>135****1786</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7349,7 +7349,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7372,7 +7372,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18333253777</t>
+          <t>183****3777</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7395,7 +7395,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15306893630</t>
+          <t>153****3630</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7418,7 +7418,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13911888618</t>
+          <t>139****8618</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7441,7 +7441,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17821117333</t>
+          <t>178****7333</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7464,7 +7464,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13911248547</t>
+          <t>139****8547</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7487,7 +7487,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15221915121</t>
+          <t>152****5121</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7510,7 +7510,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13552196092</t>
+          <t>135****6092</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7533,7 +7533,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13701026300</t>
+          <t>137****6300</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7556,7 +7556,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17634516106</t>
+          <t>176****6106</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7579,7 +7579,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13260013317</t>
+          <t>132****3317</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7602,7 +7602,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>13918718425</t>
+          <t>139****8425</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -7625,7 +7625,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13601206474</t>
+          <t>136****6474</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -7648,7 +7648,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>13611126869</t>
+          <t>136****6869</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -7671,7 +7671,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18500780039</t>
+          <t>185****0039</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -7694,7 +7694,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>15045410228</t>
+          <t>150****0228</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7717,7 +7717,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17717810024</t>
+          <t>177****0024</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7740,7 +7740,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>18710009180</t>
+          <t>187****9180</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7763,7 +7763,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>13811276310</t>
+          <t>138****6310</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7786,7 +7786,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>13808091475</t>
+          <t>138****1475</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7809,7 +7809,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>17306918759</t>
+          <t>173****8759</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -7832,7 +7832,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18111963268</t>
+          <t>181****3268</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -7855,7 +7855,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>15210286391</t>
+          <t>152****6391</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -7878,7 +7878,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>17710058506</t>
+          <t>177****8506</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7901,7 +7901,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13818538850</t>
+          <t>138****8850</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7924,7 +7924,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>18101894558</t>
+          <t>181****4558</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -7947,7 +7947,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15010512034</t>
+          <t>150****2034</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7970,7 +7970,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>13901281279</t>
+          <t>139****1279</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7993,7 +7993,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17790714180</t>
+          <t>177****4180</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -8016,7 +8016,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>13161940631</t>
+          <t>131****0631</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -8039,7 +8039,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15566742107</t>
+          <t>155****2107</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -8062,7 +8062,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19520415481</t>
+          <t>195****5481</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8085,7 +8085,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>13693230356</t>
+          <t>136****0356</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8108,7 +8108,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>15905889267</t>
+          <t>159****9267</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8131,7 +8131,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17611641312</t>
+          <t>176****1312</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8154,7 +8154,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>18339470337</t>
+          <t>183****0337</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -8177,7 +8177,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15295165686</t>
+          <t>152****5686</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -8200,7 +8200,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>18260924787</t>
+          <t>182****4787</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -8223,7 +8223,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17503270657</t>
+          <t>175****0657</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -8246,7 +8246,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>13030302041</t>
+          <t>130****2041</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -8269,7 +8269,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13081831002</t>
+          <t>130****1002</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -8292,7 +8292,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>18010058870</t>
+          <t>180****8870</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -8315,7 +8315,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>18917385750</t>
+          <t>189****5750</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -8338,7 +8338,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15600257975</t>
+          <t>156****7975</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -8361,7 +8361,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>17778161185</t>
+          <t>177****1185</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -8384,7 +8384,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15738922471</t>
+          <t>157****2471</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -8407,7 +8407,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>17310230575</t>
+          <t>173****0575</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -8430,7 +8430,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17610855720</t>
+          <t>176****5720</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -8453,7 +8453,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13261316998</t>
+          <t>132****6998</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -8476,7 +8476,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13008080555</t>
+          <t>130****0555</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -8499,7 +8499,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18618381620</t>
+          <t>186****1620</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -8522,7 +8522,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17361368276</t>
+          <t>173****8276</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -8545,7 +8545,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15161233164</t>
+          <t>151****3164</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -8568,7 +8568,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13681499192</t>
+          <t>136****9192</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -8591,7 +8591,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13681998096</t>
+          <t>136****8096</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -8614,7 +8614,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13683369780</t>
+          <t>136****9780</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -8637,7 +8637,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>13616040095</t>
+          <t>136****0095</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -8660,7 +8660,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>13601173957</t>
+          <t>136****3957</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -8683,7 +8683,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>13911622333</t>
+          <t>139****2333</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -8706,7 +8706,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18519083953</t>
+          <t>185****3953</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -8729,7 +8729,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>18393823556</t>
+          <t>183****3556</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -8752,7 +8752,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>19261039142</t>
+          <t>192****9142</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -8775,7 +8775,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>13810838107</t>
+          <t>138****8107</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -8798,7 +8798,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>13521708230</t>
+          <t>135****8230</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -8821,7 +8821,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>19229850173</t>
+          <t>192****0173</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8844,7 +8844,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>13716008576</t>
+          <t>137****8576</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -8867,7 +8867,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>13436441080</t>
+          <t>134****1080</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -8890,7 +8890,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15300039878</t>
+          <t>153****9878</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -8913,7 +8913,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>13001195866</t>
+          <t>130****5866</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8936,7 +8936,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>18860171876</t>
+          <t>188****1876</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -8959,7 +8959,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>19198998488</t>
+          <t>191****8488</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -8982,7 +8982,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>17759588798</t>
+          <t>177****8798</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -9005,7 +9005,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>13162909498</t>
+          <t>131****9498</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -9028,7 +9028,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>13311377412</t>
+          <t>133****7412</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -9051,7 +9051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>18210230765</t>
+          <t>182****0765</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -9074,7 +9074,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>13240108794</t>
+          <t>132****8794</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -9097,7 +9097,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18239463963</t>
+          <t>182****3963</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -9120,7 +9120,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>15600284358</t>
+          <t>156****4358</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -9143,7 +9143,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>17701085375</t>
+          <t>177****5375</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -9166,7 +9166,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>13916625693</t>
+          <t>139****5693</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -9189,7 +9189,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>19150369723</t>
+          <t>191****9723</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -9212,7 +9212,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>13911331771</t>
+          <t>139****1771</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -9235,7 +9235,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18055131452</t>
+          <t>180****1452</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -9258,7 +9258,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>18519663666</t>
+          <t>185****3666</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -9281,7 +9281,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18262299666</t>
+          <t>182****9666</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -9304,7 +9304,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>13910762889</t>
+          <t>139****2889</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -9327,7 +9327,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>13581501297</t>
+          <t>135****1297</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -9350,7 +9350,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>15184398777</t>
+          <t>151****8777</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -9373,7 +9373,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>13939423148</t>
+          <t>139****3148</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -9396,7 +9396,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>13718722040</t>
+          <t>137****2040</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -9419,7 +9419,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>13311279158</t>
+          <t>133****9158</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -9442,7 +9442,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>19828386370</t>
+          <t>198****6370</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -9465,7 +9465,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15933476673</t>
+          <t>159****6673</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -9488,7 +9488,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>18953537966</t>
+          <t>189****7966</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -9511,7 +9511,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>15727385006</t>
+          <t>157****5006</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -9534,7 +9534,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>15373279618</t>
+          <t>153****9618</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -9557,7 +9557,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>15930247284</t>
+          <t>159****7284</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -9580,7 +9580,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>13910231980</t>
+          <t>139****1980</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -9603,7 +9603,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>17359032093</t>
+          <t>173****2093</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -9626,7 +9626,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15201447010</t>
+          <t>152****7010</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -9649,7 +9649,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>13917486689</t>
+          <t>139****6689</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -9672,7 +9672,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>13810402021</t>
+          <t>138****2021</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -9695,7 +9695,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>13141307777</t>
+          <t>131****7777</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -9718,7 +9718,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>13241952989</t>
+          <t>132****2989</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9741,7 +9741,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>13385309523</t>
+          <t>133****9523</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -9764,7 +9764,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>13811725368</t>
+          <t>138****5368</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -9787,7 +9787,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>13358299510</t>
+          <t>133****9510</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -9810,7 +9810,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>18810950563</t>
+          <t>188****0563</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -9833,7 +9833,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15810190917</t>
+          <t>158****0917</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -9856,7 +9856,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>18500798860</t>
+          <t>185****8860</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -9879,7 +9879,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>13301385865</t>
+          <t>133****5865</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -9902,7 +9902,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>15601881159</t>
+          <t>156****1159</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -9925,7 +9925,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>13753569783</t>
+          <t>137****9783</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -9948,7 +9948,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>13120237385</t>
+          <t>131****7385</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -9971,7 +9971,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>13705083183</t>
+          <t>137****3183</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -9994,7 +9994,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>13146262311</t>
+          <t>131****2311</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -10017,7 +10017,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>18616502346</t>
+          <t>186****2346</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -10040,7 +10040,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>17380008867</t>
+          <t>173****8867</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -10063,7 +10063,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>18612596015</t>
+          <t>186****6015</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -10086,7 +10086,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>15809317030</t>
+          <t>158****7030</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -10109,7 +10109,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15531182175</t>
+          <t>155****2175</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -10132,7 +10132,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>18613879907</t>
+          <t>186****9907</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -10155,7 +10155,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>18500858779</t>
+          <t>185****8779</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -10178,7 +10178,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>17630974613</t>
+          <t>176****4613</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -10201,7 +10201,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>13811732133</t>
+          <t>138****2133</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -10224,7 +10224,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>17601273516</t>
+          <t>176****3516</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -10247,7 +10247,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>17301121619</t>
+          <t>173****1619</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -10270,7 +10270,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>13621123138</t>
+          <t>136****3138</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -10293,7 +10293,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>13701397707</t>
+          <t>137****7707</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -10316,7 +10316,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>13261670129</t>
+          <t>132****0129</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -10339,7 +10339,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>13261857667</t>
+          <t>132****7667</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -10362,7 +10362,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>18210745020</t>
+          <t>182****5020</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -10385,7 +10385,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>15081204266</t>
+          <t>150****4266</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -10408,7 +10408,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>15811336178</t>
+          <t>158****6178</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -10431,7 +10431,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>18220538460</t>
+          <t>182****8460</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -10454,7 +10454,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>15545620971</t>
+          <t>155****0971</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -10477,7 +10477,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>15601218618</t>
+          <t>156****8618</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -10500,7 +10500,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>18210255124</t>
+          <t>182****5124</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -10523,7 +10523,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>15048686819</t>
+          <t>150****6819</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -10546,7 +10546,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>13910903939</t>
+          <t>139****3939</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -10569,7 +10569,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>13959152114</t>
+          <t>139****2114</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -10592,7 +10592,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>18905929861</t>
+          <t>189****9861</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -10615,7 +10615,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>18510008593</t>
+          <t>185****8593</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -10638,7 +10638,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>13810206422</t>
+          <t>138****6422</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -10661,7 +10661,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>15754862672</t>
+          <t>157****2672</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -10684,7 +10684,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>18766220138</t>
+          <t>187****0138</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -10707,7 +10707,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>18310182363</t>
+          <t>183****2363</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -10730,7 +10730,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>13683024467</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -10753,7 +10753,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>13321178267</t>
+          <t>133****8267</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -10776,7 +10776,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>18610167763</t>
+          <t>186****7763</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -10799,7 +10799,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>13701969018</t>
+          <t>137****9018</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -10822,7 +10822,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>18811680651</t>
+          <t>188****0651</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -10845,7 +10845,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>15827101791</t>
+          <t>158****1791</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -10868,7 +10868,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>13520426123</t>
+          <t>135****6123</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -10891,7 +10891,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>13761268200</t>
+          <t>137****8200</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -10914,7 +10914,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>13671927686</t>
+          <t>136****7686</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -10937,7 +10937,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15530315870</t>
+          <t>155****5870</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -10960,7 +10960,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>15835108077</t>
+          <t>158****8077</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -10983,7 +10983,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>13721956196</t>
+          <t>137****6196</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -11006,7 +11006,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>13611197680</t>
+          <t>136****7680</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -11029,7 +11029,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>18732812468</t>
+          <t>187****2468</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -11052,7 +11052,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>13552155833</t>
+          <t>135****5833</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -11075,7 +11075,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>13166300779</t>
+          <t>131****0779</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -11098,7 +11098,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>18210232186</t>
+          <t>182****2186</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -11121,7 +11121,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>15011282507</t>
+          <t>150****2507</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -11144,7 +11144,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>18645297329</t>
+          <t>186****7329</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -11167,7 +11167,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>13321180833</t>
+          <t>133****0833</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -11190,7 +11190,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>15618709987</t>
+          <t>156****9987</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -11213,7 +11213,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>15055641059</t>
+          <t>150****1059</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -11236,7 +11236,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>13681483984</t>
+          <t>136****3984</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -11259,7 +11259,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>17761519191</t>
+          <t>177****9191</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -11282,7 +11282,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>17600176165</t>
+          <t>176****6165</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -11305,7 +11305,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18152584730</t>
+          <t>181****4730</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -11328,7 +11328,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>15759221390</t>
+          <t>157****1390</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>13611297697</t>
+          <t>136****7697</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -11374,7 +11374,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>13755325947</t>
+          <t>137****5947</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -11397,7 +11397,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>13810575885</t>
+          <t>138****5885</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -11420,7 +11420,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>15801252585</t>
+          <t>158****2585</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -11443,7 +11443,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>13079611389</t>
+          <t>130****1389</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -11466,7 +11466,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>18116660220</t>
+          <t>181****0220</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -11489,7 +11489,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>18519660990</t>
+          <t>185****0990</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -11512,7 +11512,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>18039040128</t>
+          <t>180****0128</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -11535,7 +11535,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>15811249672</t>
+          <t>158****9672</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -11558,7 +11558,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>13488619695</t>
+          <t>134****9695</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -11581,7 +11581,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>18532310659</t>
+          <t>185****0659</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -11604,7 +11604,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>15600233213</t>
+          <t>156****3213</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -11627,7 +11627,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>13801273055</t>
+          <t>138****3055</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -11650,7 +11650,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>13911751260</t>
+          <t>139****1260</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -11673,7 +11673,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>13810429143</t>
+          <t>138****9143</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -11696,7 +11696,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>18510353525</t>
+          <t>185****3525</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -11719,7 +11719,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>13701028544</t>
+          <t>137****8544</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -11742,7 +11742,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>13501280368</t>
+          <t>135****0368</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -11765,7 +11765,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>13290625981</t>
+          <t>132****5981</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -11788,7 +11788,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>18682918886</t>
+          <t>186****8886</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -11811,7 +11811,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>13331991773</t>
+          <t>133****1773</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -11834,7 +11834,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>13811874190</t>
+          <t>138****4190</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -11857,7 +11857,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>13905910511</t>
+          <t>139****0511</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -11880,7 +11880,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>18301163023</t>
+          <t>183****3023</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -11903,7 +11903,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>18622040086</t>
+          <t>186****0086</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -11926,7 +11926,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>15942053555</t>
+          <t>159****3555</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -11949,7 +11949,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>13607587000</t>
+          <t>136****7000</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -11972,7 +11972,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>18310997088</t>
+          <t>183****7088</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -11995,7 +11995,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>13601188623</t>
+          <t>136****8623</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -12018,7 +12018,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>13718093269</t>
+          <t>137****3269</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -12041,7 +12041,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>18678155539</t>
+          <t>186****5539</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -12064,7 +12064,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>13716243870</t>
+          <t>137****3870</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -12087,7 +12087,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>13601208355</t>
+          <t>136****8355</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -12110,7 +12110,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>13381137800</t>
+          <t>133****7800</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -12133,7 +12133,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>13001207217</t>
+          <t>130****7217</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -12156,7 +12156,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>15210414185</t>
+          <t>152****4185</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -12179,7 +12179,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>18610099262</t>
+          <t>186****9262</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -12202,7 +12202,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>15821145415</t>
+          <t>158****5415</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -12225,7 +12225,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13681746167</t>
+          <t>136****6167</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -12248,7 +12248,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>15827490045</t>
+          <t>158****0045</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -12271,7 +12271,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>13671897012</t>
+          <t>136****7012</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -12294,7 +12294,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>15116938941</t>
+          <t>151****8941</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -12317,7 +12317,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>13912898742</t>
+          <t>139****8742</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -12340,7 +12340,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>18018519252</t>
+          <t>180****9252</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -12363,7 +12363,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>13488647740</t>
+          <t>134****7740</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -12386,7 +12386,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>18611820647</t>
+          <t>186****0647</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -12409,7 +12409,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>13764294612</t>
+          <t>137****4612</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -12432,7 +12432,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>13525256200</t>
+          <t>135****6200</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -12455,7 +12455,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>18817312560</t>
+          <t>188****2560</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -12478,7 +12478,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>15175064705</t>
+          <t>151****4705</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -12501,7 +12501,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>15321160352</t>
+          <t>153****0352</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -12524,7 +12524,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>13366718929</t>
+          <t>133****8929</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -12547,7 +12547,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>13122359792</t>
+          <t>131****9792</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -12570,7 +12570,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>13699270194</t>
+          <t>136****0194</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -12593,7 +12593,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>15910355812</t>
+          <t>159****5812</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -12616,7 +12616,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>17605276848</t>
+          <t>176****6848</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -12639,7 +12639,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>19107136807</t>
+          <t>191****6807</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -12662,7 +12662,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>13269486610</t>
+          <t>132****6610</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -12685,7 +12685,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>13581568460</t>
+          <t>135****8460</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -12708,7 +12708,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>18311484501</t>
+          <t>183****4501</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -12731,7 +12731,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>16632476171</t>
+          <t>166****6171</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -12754,7 +12754,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>18332082244</t>
+          <t>183****2244</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -12777,7 +12777,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>18439401112</t>
+          <t>184****1112</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -12800,7 +12800,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>18610749241</t>
+          <t>186****9241</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -12823,7 +12823,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>18601950753</t>
+          <t>186****0753</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -12846,7 +12846,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>18120234785</t>
+          <t>181****4785</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -12869,7 +12869,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>18627131818</t>
+          <t>186****1818</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -12892,7 +12892,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>18852895135</t>
+          <t>188****5135</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -12915,7 +12915,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>13590149932</t>
+          <t>135****9932</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -12938,7 +12938,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>16630799321</t>
+          <t>166****9321</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -12961,7 +12961,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>18612939929</t>
+          <t>186****9929</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -12984,7 +12984,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>15810955032</t>
+          <t>158****5032</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -13007,7 +13007,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>18249067191</t>
+          <t>182****7191</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -13030,7 +13030,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>18168578530</t>
+          <t>181****8530</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -13053,7 +13053,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>18001911598</t>
+          <t>180****1598</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -13076,7 +13076,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>18910611506</t>
+          <t>189****1506</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -13099,7 +13099,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>18281859693</t>
+          <t>182****9693</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -13122,7 +13122,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>15011528215</t>
+          <t>150****8215</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -13145,7 +13145,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>13910381032</t>
+          <t>139****1032</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -13168,7 +13168,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>18210641792</t>
+          <t>182****1792</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -13191,7 +13191,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>18301601370</t>
+          <t>183****1370</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -13214,7 +13214,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>18803141991</t>
+          <t>188****1991</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -13237,7 +13237,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>18801226370</t>
+          <t>188****6370</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -13260,7 +13260,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>15198805389</t>
+          <t>151****5389</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -13283,7 +13283,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>13520202168</t>
+          <t>135****2168</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -13306,7 +13306,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>15010227544</t>
+          <t>150****7544</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -13329,7 +13329,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>18311095502</t>
+          <t>183****5502</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -13352,7 +13352,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>13810028787</t>
+          <t>138****8787</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -13375,7 +13375,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>18601249195</t>
+          <t>186****9195</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -13398,7 +13398,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>13811728032</t>
+          <t>138****8032</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -13421,7 +13421,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>15010269325</t>
+          <t>150****9325</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -13444,7 +13444,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>13466605322</t>
+          <t>134****5322</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -13467,7 +13467,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>18633329155</t>
+          <t>186****9155</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -13490,7 +13490,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>15313222127</t>
+          <t>153****2127</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -13513,7 +13513,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>13395905290</t>
+          <t>133****5290</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -13536,7 +13536,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>18513106772</t>
+          <t>185****6772</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -13559,7 +13559,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>13817928936</t>
+          <t>138****8936</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -13582,7 +13582,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>18612798646</t>
+          <t>186****8646</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -13605,7 +13605,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>13521014567</t>
+          <t>135****4567</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -13628,7 +13628,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>18385781992</t>
+          <t>183****1992</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -13651,7 +13651,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>15901135216</t>
+          <t>159****5216</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -13674,7 +13674,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>18629277159</t>
+          <t>186****7159</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -13697,7 +13697,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>13806061864</t>
+          <t>138****1864</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -13720,7 +13720,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>15195994197</t>
+          <t>151****4197</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -13743,7 +13743,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>18501369159</t>
+          <t>185****9159</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -13766,7 +13766,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>13810586912</t>
+          <t>138****6912</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -13789,7 +13789,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>15300325001</t>
+          <t>153****5001</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -13812,7 +13812,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>18611734699</t>
+          <t>186****4699</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -13835,7 +13835,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>18760005116</t>
+          <t>187****5116</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -13858,7 +13858,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>13472054605</t>
+          <t>134****4605</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -13881,7 +13881,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>17369696661</t>
+          <t>173****6661</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -13904,7 +13904,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>13681592680</t>
+          <t>136****2680</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -13927,7 +13927,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>13716632275</t>
+          <t>137****2275</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -13950,7 +13950,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>13520774258</t>
+          <t>135****4258</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -13973,7 +13973,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>13811316899</t>
+          <t>138****6899</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -13996,7 +13996,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>13522251340</t>
+          <t>135****1340</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -14019,7 +14019,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>18500091875</t>
+          <t>185****1875</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -14042,7 +14042,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>18229477205</t>
+          <t>182****7205</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -14065,7 +14065,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>13391528767</t>
+          <t>133****8767</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -14088,7 +14088,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>15732610800</t>
+          <t>157****0800</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -14111,7 +14111,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>18201157053</t>
+          <t>182****7053</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -14134,7 +14134,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>13520836132</t>
+          <t>135****6132</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -14157,7 +14157,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>18618323301</t>
+          <t>186****3301</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -14180,7 +14180,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>18621576622</t>
+          <t>186****6622</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -14203,7 +14203,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>13611130326</t>
+          <t>136****0326</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -14226,7 +14226,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>18334794466</t>
+          <t>183****4466</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -14249,7 +14249,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>13301851456</t>
+          <t>133****1456</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -14272,7 +14272,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>19061587978</t>
+          <t>190****7978</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -14295,7 +14295,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>18336002603</t>
+          <t>183****2603</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -14318,7 +14318,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>15201352750</t>
+          <t>152****2750</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -14341,7 +14341,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>13810670553</t>
+          <t>138****0553</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -14364,7 +14364,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>17778169607</t>
+          <t>177****9607</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -14387,7 +14387,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>15902810226</t>
+          <t>159****0226</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -14410,7 +14410,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>18910373510</t>
+          <t>189****3510</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -14433,7 +14433,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>13901042931</t>
+          <t>139****2931</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -14456,7 +14456,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>18159967089</t>
+          <t>181****7089</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -14479,7 +14479,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>13636631536</t>
+          <t>136****1536</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -14502,7 +14502,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>13998606813</t>
+          <t>139****6813</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -14525,7 +14525,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>13911397295</t>
+          <t>139****7295</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -14548,7 +14548,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>13665252313</t>
+          <t>136****2313</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -14571,7 +14571,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>18001391086</t>
+          <t>180****1086</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -14594,7 +14594,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>13910824041</t>
+          <t>139****4041</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -14617,7 +14617,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>13913933990</t>
+          <t>139****3990</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -14640,7 +14640,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>13910242343</t>
+          <t>139****2343</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -14663,7 +14663,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>18721970468</t>
+          <t>187****0468</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -14686,7 +14686,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>13691576168</t>
+          <t>136****6168</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -14709,7 +14709,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>13581688824</t>
+          <t>135****8824</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -14732,7 +14732,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>13521172823</t>
+          <t>135****2823</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -14755,7 +14755,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>16604148777</t>
+          <t>166****8777</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -14778,7 +14778,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>18088286821</t>
+          <t>180****6821</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -14801,7 +14801,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>15300636118</t>
+          <t>153****6118</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -14824,7 +14824,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>17702295481</t>
+          <t>177****5481</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -14847,7 +14847,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>18131408390</t>
+          <t>181****8390</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -14870,7 +14870,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>13520433774</t>
+          <t>135****3774</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -14893,7 +14893,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>13718700892</t>
+          <t>137****0892</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -14916,7 +14916,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>18111968858</t>
+          <t>181****8858</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -14939,7 +14939,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>13911918137</t>
+          <t>139****8137</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17732888060</t>
+          <t>177****8060</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13911290670</t>
+          <t>139****0670</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13811162976</t>
+          <t>138****2976</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13810028787</t>
+          <t>138****8787</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13552196092</t>
+          <t>135****6092</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18513106772</t>
+          <t>185****6772</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13520836132</t>
+          <t>135****6132</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13269486610</t>
+          <t>132****6610</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13911397295</t>
+          <t>139****7295</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17761519191</t>
+          <t>177****9191</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15378954286</t>
+          <t>153****4286</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15663258696</t>
+          <t>156****8696</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13521788196</t>
+          <t>135****8196</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15330073070</t>
+          <t>153****3070</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17610855720</t>
+          <t>176****5720</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15210286391</t>
+          <t>152****6391</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17503270657</t>
+          <t>175****0657</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17611641312</t>
+          <t>176****1312</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15930247284</t>
+          <t>159****7284</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13681592680</t>
+          <t>136****2680</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13810429143</t>
+          <t>138****9143</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13611197680</t>
+          <t>136****7680</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18613879907</t>
+          <t>186****9907</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15010227544</t>
+          <t>150****7544</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15210414185</t>
+          <t>152****4185</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13811874190</t>
+          <t>138****4190</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13811725368</t>
+          <t>138****5368</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15801252585</t>
+          <t>158****2585</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13079611389</t>
+          <t>130****1389</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13810586912</t>
+          <t>138****6912</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18239463963</t>
+          <t>182****3963</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18210745020</t>
+          <t>182****5020</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15011282507</t>
+          <t>150****2507</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13293019486</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15701060983</t>
+          <t>157****0983</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13521234380</t>
+          <t>135****4380</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15227416428</t>
+          <t>152****6428</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13260013317</t>
+          <t>132****3317</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15905889267</t>
+          <t>159****9267</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17778161185</t>
+          <t>177****1185</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17361368276</t>
+          <t>173****8276</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13801273055</t>
+          <t>138****3055</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18055131452</t>
+          <t>180****1452</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13581688824</t>
+          <t>135****8824</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13716243870</t>
+          <t>137****3870</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15809317030</t>
+          <t>158****7030</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>13601208355</t>
+          <t>136****8355</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>18500858779</t>
+          <t>185****8779</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18501369159</t>
+          <t>185****9159</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18439401112</t>
+          <t>184****1112</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13466605322</t>
+          <t>134****5322</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18810950563</t>
+          <t>188****0563</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -16555,7 +16555,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13525256200</t>
+          <t>135****6200</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15373279618</t>
+          <t>153****9618</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18333253777</t>
+          <t>183****3777</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17369696661</t>
+          <t>173****6661</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15081204266</t>
+          <t>150****4266</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18168578530</t>
+          <t>181****8530</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>18601249195</t>
+          <t>186****9195</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13901042931</t>
+          <t>139****2931</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13810206422</t>
+          <t>138****6422</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18511226888</t>
+          <t>185****6888</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18245704734</t>
+          <t>182****4734</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18710009180</t>
+          <t>187****9180</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13911622333</t>
+          <t>139****2333</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15600233213</t>
+          <t>156****3213</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>18039040128</t>
+          <t>180****0128</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>18645297329</t>
+          <t>186****7329</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>18500091875</t>
+          <t>185****1875</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13240108794</t>
+          <t>132****8794</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15116938941</t>
+          <t>151****8941</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18610749241</t>
+          <t>186****9241</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13161289910</t>
+          <t>131****9910</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>17790714180</t>
+          <t>177****4180</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>15300325001</t>
+          <t>153****5001</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13141307777</t>
+          <t>131****7777</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>13171607183</t>
+          <t>131****7183</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>17710058506</t>
+          <t>177****8506</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>15010269325</t>
+          <t>150****9325</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>17883180691</t>
+          <t>178****0691</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13808091475</t>
+          <t>138****1475</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>18917385750</t>
+          <t>189****5750</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15601881159</t>
+          <t>156****1159</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>18510008593</t>
+          <t>185****8593</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13916625693</t>
+          <t>139****5693</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>18001911598</t>
+          <t>180****1598</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>15618709987</t>
+          <t>156****9987</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13764294612</t>
+          <t>137****4612</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>13601188623</t>
+          <t>136****8623</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15045410228</t>
+          <t>150****0228</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>13391528767</t>
+          <t>133****8767</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13911331771</t>
+          <t>139****1771</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13918718425</t>
+          <t>139****8425</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13681998096</t>
+          <t>136****8096</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>18220538460</t>
+          <t>182****8460</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18678155539</t>
+          <t>186****5539</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>18817312560</t>
+          <t>188****2560</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13301851456</t>
+          <t>133****1456</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13008080555</t>
+          <t>130****0555</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>18682918886</t>
+          <t>186****8886</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13241952989</t>
+          <t>132****2989</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13811728032</t>
+          <t>138****8032</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13910762889</t>
+          <t>139****2889</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>13910242343</t>
+          <t>139****2343</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>18629277159</t>
+          <t>186****7159</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>13683369780</t>
+          <t>136****9780</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13311377412</t>
+          <t>133****7412</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13301385865</t>
+          <t>133****5865</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>15601218618</t>
+          <t>156****8618</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15891781131</t>
+          <t>158****1131</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15733359639</t>
+          <t>157****9639</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>18766220138</t>
+          <t>187****0138</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19198998488</t>
+          <t>191****8488</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15727385006</t>
+          <t>157****5006</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>18152584730</t>
+          <t>181****4730</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -18999,7 +18999,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>18610932185</t>
+          <t>186****2185</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>13030302041</t>
+          <t>130****2041</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13665252313</t>
+          <t>136****2313</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>18910611506</t>
+          <t>189****1506</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -19129,7 +19129,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13716632275</t>
+          <t>137****2275</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>18611820647</t>
+          <t>186****0647</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>15201352750</t>
+          <t>152****2750</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13001195866</t>
+          <t>130****5866</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>13911246265</t>
+          <t>139****6265</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13701026300</t>
+          <t>137****6300</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>13001207217</t>
+          <t>130****7217</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>18249067191</t>
+          <t>182****7191</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13913933990</t>
+          <t>139****3990</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15754862672</t>
+          <t>157****2672</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>17701085375</t>
+          <t>177****5375</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>15821145415</t>
+          <t>158****5415</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>13761268200</t>
+          <t>137****8200</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>18010058870</t>
+          <t>180****8870</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>13521172823</t>
+          <t>135****2823</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>18811031085</t>
+          <t>188****1085</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>18018519252</t>
+          <t>180****9252</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>16630799321</t>
+          <t>166****9321</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>15311196683</t>
+          <t>153****6683</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>15521301582</t>
+          <t>155****1582</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>13581568460</t>
+          <t>135****8460</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -19909,7 +19909,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>13321180833</t>
+          <t>133****0833</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>18334794466</t>
+          <t>183****4466</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>13581501297</t>
+          <t>135****1297</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>18801226370</t>
+          <t>188****6370</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -20065,7 +20065,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>13269815521</t>
+          <t>132****5521</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>13810838107</t>
+          <t>138****8107</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>13621123138</t>
+          <t>136****3138</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>13910903939</t>
+          <t>139****3939</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>18500798860</t>
+          <t>185****8860</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>13520202168</t>
+          <t>135****2168</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>13811316899</t>
+          <t>138****6899</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>17601663766</t>
+          <t>176****3766</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>13681499192</t>
+          <t>136****9192</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>13611297697</t>
+          <t>136****7697</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>15198805389</t>
+          <t>151****5389</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>13472054605</t>
+          <t>134****4605</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>17778169607</t>
+          <t>177****9607</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>18811680651</t>
+          <t>188****0651</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>13607587000</t>
+          <t>136****7000</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>13810670553</t>
+          <t>138****0553</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -20585,7 +20585,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>15835108077</t>
+          <t>158****8077</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>13366718929</t>
+          <t>133****8929</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>15942053555</t>
+          <t>159****3555</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>13311279158</t>
+          <t>133****9158</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>18131408390</t>
+          <t>181****8390</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>18301163023</t>
+          <t>183****3023</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>18210230765</t>
+          <t>182****0765</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>13699270194</t>
+          <t>136****0194</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>13611130326</t>
+          <t>136****0326</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>18610099262</t>
+          <t>186****9262</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>15201447010</t>
+          <t>152****7010</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>18510353525</t>
+          <t>185****3525</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>13520433774</t>
+          <t>135****3774</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>19107136807</t>
+          <t>191****6807</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>18332082244</t>
+          <t>183****2244</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -21079,7 +21079,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>19828386370</t>
+          <t>198****6370</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>19150369723</t>
+          <t>191****9723</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>15306893630</t>
+          <t>153****3630</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -21209,7 +21209,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>18310182363</t>
+          <t>183****2363</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>18311484501</t>
+          <t>183****4501</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -21261,7 +21261,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>15810190917</t>
+          <t>158****0917</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>15175064705</t>
+          <t>151****4705</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>13911751260</t>
+          <t>139****1260</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>18088286821</t>
+          <t>180****6821</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>17630974613</t>
+          <t>176****4613</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>13681483984</t>
+          <t>136****3984</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>15161233164</t>
+          <t>151****3164</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>13611126869</t>
+          <t>136****6869</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>15321160352</t>
+          <t>153****0352</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>13488619695</t>
+          <t>134****9695</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -21573,7 +21573,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>17605276848</t>
+          <t>176****6848</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>18201157053</t>
+          <t>182****7053</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>18210255124</t>
+          <t>182****5124</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>18611734699</t>
+          <t>186****4699</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -21703,7 +21703,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>13520774258</t>
+          <t>135****4258</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>18116660220</t>
+          <t>181****0220</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>13911248547</t>
+          <t>139****8547</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -21885,7 +21885,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>18519083953</t>
+          <t>185****3953</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>18219829757</t>
+          <t>182****9757</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>15195994197</t>
+          <t>151****4197</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -21989,7 +21989,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>18159967089</t>
+          <t>181****7089</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -22041,7 +22041,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>13717797690</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>13161940631</t>
+          <t>131****0631</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -22119,7 +22119,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>18519660990</t>
+          <t>185****0990</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>13721956196</t>
+          <t>137****6196</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>13601206474</t>
+          <t>136****6474</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>13601173957</t>
+          <t>136****3957</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>15811249672</t>
+          <t>158****9672</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>15732610800</t>
+          <t>157****0800</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>19261039142</t>
+          <t>192****9142</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>13081831002</t>
+          <t>130****1002</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>18311095502</t>
+          <t>183****5502</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>13261670129</t>
+          <t>132****0129</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>18612596015</t>
+          <t>186****6015</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>13436441080</t>
+          <t>134****1080</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>18120234785</t>
+          <t>181****4785</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -22561,7 +22561,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>17278102448</t>
+          <t>172****2448</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>15738922471</t>
+          <t>157****2471</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>18610167763</t>
+          <t>186****7763</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>13753569783</t>
+          <t>137****9783</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>18262299666</t>
+          <t>182****9666</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>15759221390</t>
+          <t>157****1390</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -22743,7 +22743,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>17359032093</t>
+          <t>173****2093</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -22847,7 +22847,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>18803141991</t>
+          <t>188****1991</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>13290625981</t>
+          <t>132****5981</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>13911918137</t>
+          <t>139****8137</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>13552155833</t>
+          <t>135****5833</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>13879686023</t>
+          <t>138****6023</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -23081,7 +23081,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>13705083183</t>
+          <t>137****3183</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>18860171876</t>
+          <t>188****1876</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -23185,7 +23185,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>15827490045</t>
+          <t>158****0045</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>13755325947</t>
+          <t>137****5947</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -23263,7 +23263,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -23315,7 +23315,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>17601273516</t>
+          <t>176****3516</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>18519663666</t>
+          <t>185****3666</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>13522251340</t>
+          <t>135****1340</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>18532310659</t>
+          <t>185****0659</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>18001391086</t>
+          <t>180****1086</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>13718700892</t>
+          <t>137****0892</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>18930090939</t>
+          <t>189****0939</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>13681746167</t>
+          <t>136****6167</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>18616502346</t>
+          <t>186****2346</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>17380008867</t>
+          <t>173****8867</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>13671897012</t>
+          <t>136****7012</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -23731,7 +23731,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>13917486689</t>
+          <t>139****6689</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>18953537966</t>
+          <t>189****7966</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -23783,7 +23783,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -23809,7 +23809,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>15010512034</t>
+          <t>150****2034</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>13321178267</t>
+          <t>133****8267</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>15827101791</t>
+          <t>158****1791</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>16604148777</t>
+          <t>166****8777</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>15811336178</t>
+          <t>158****6178</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>13905910511</t>
+          <t>139****0511</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>18905929861</t>
+          <t>189****9861</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>13806061864</t>
+          <t>138****1864</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>15221915121</t>
+          <t>152****5121</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>13636631536</t>
+          <t>136****1536</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>18852895135</t>
+          <t>188****5135</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -24303,7 +24303,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>13998606813</t>
+          <t>139****6813</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>13817928936</t>
+          <t>138****8936</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>13331991773</t>
+          <t>133****1773</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -24381,7 +24381,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>18618381620</t>
+          <t>186****1620</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -24485,7 +24485,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>13381137800</t>
+          <t>133****7800</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>13120237385</t>
+          <t>131****7385</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>13691576168</t>
+          <t>136****6168</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -24615,7 +24615,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>15300039878</t>
+          <t>153****9878</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -24641,7 +24641,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>13701397707</t>
+          <t>137****7707</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>15313222127</t>
+          <t>153****2127</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -24693,7 +24693,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>15201123395</t>
+          <t>152****3395</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>18393823556</t>
+          <t>183****3556</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>13521708230</t>
+          <t>135****8230</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>13939423148</t>
+          <t>139****3148</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -24849,7 +24849,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>13395905290</t>
+          <t>133****5290</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -24901,7 +24901,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>17717810024</t>
+          <t>177****0024</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>13912898742</t>
+          <t>139****8742</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>13616040095</t>
+          <t>136****0095</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>19520415481</t>
+          <t>195****5481</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>15933476673</t>
+          <t>159****6673</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>18622040086</t>
+          <t>186****0086</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -25265,7 +25265,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>13237413419</t>
+          <t>132****3419</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -25317,7 +25317,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>13901281279</t>
+          <t>139****1279</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -25343,7 +25343,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>18601950753</t>
+          <t>186****0753</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>18612939929</t>
+          <t>186****9929</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>18301601370</t>
+          <t>183****1370</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>18732812468</t>
+          <t>187****2468</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>13716008576</t>
+          <t>137****8576</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>15600284358</t>
+          <t>156****4358</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -25525,7 +25525,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>19061587978</t>
+          <t>190****7978</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -25551,7 +25551,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -25577,7 +25577,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>15910355812</t>
+          <t>159****5812</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -25603,7 +25603,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>18210641792</t>
+          <t>182****1792</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -25629,7 +25629,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>13146262311</t>
+          <t>131****2311</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -25707,7 +25707,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>18760005116</t>
+          <t>187****5116</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -25733,7 +25733,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -25785,7 +25785,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13358299510</t>
+          <t>133****9510</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -25837,7 +25837,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -25863,7 +25863,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>18336002603</t>
+          <t>183****2603</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -25889,7 +25889,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>18281859693</t>
+          <t>182****9693</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>15295165686</t>
+          <t>152****5686</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -26019,7 +26019,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>15901135216</t>
+          <t>159****5216</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>13810402021</t>
+          <t>138****2021</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -26123,7 +26123,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>17821117333</t>
+          <t>178****7333</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>19229850173</t>
+          <t>192****0173</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>13590149932</t>
+          <t>135****9932</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -26227,7 +26227,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>13261857667</t>
+          <t>132****7667</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -26279,7 +26279,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>13910381032</t>
+          <t>139****1032</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -26357,7 +26357,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>18229477205</t>
+          <t>182****7205</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>18210182706</t>
+          <t>182****2706</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>15566742107</t>
+          <t>155****2107</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -26461,7 +26461,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>15545620971</t>
+          <t>155****0971</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16632476171</t>
+          <t>166****6171</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>17600176165</t>
+          <t>176****6165</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>13718093269</t>
+          <t>137****3269</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -26669,7 +26669,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>15600257975</t>
+          <t>156****7975</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -26721,7 +26721,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>13683024467</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -26773,7 +26773,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>13521014567</t>
+          <t>135****4567</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>13701028544</t>
+          <t>137****8544</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>13910231980</t>
+          <t>139****1980</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>13272824691</t>
+          <t>132****4691</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>18260924787</t>
+          <t>182****4787</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -27033,7 +27033,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>15397387154</t>
+          <t>153****7154</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>18210182706</t>
+          <t>182****2706</t>
         </is>
       </c>
       <c r="E465" t="n">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E466" t="n">
@@ -27111,7 +27111,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -27137,7 +27137,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>13911888618</t>
+          <t>139****8618</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -27163,7 +27163,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>13488647740</t>
+          <t>134****7740</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -27189,7 +27189,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E470" t="n">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>18210232186</t>
+          <t>182****2186</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -27241,7 +27241,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E472" t="n">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>18111963268</t>
+          <t>181****3268</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -27293,7 +27293,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E475" t="n">
@@ -27345,7 +27345,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>13718722040</t>
+          <t>137****2040</t>
         </is>
       </c>
       <c r="E476" t="n">
@@ -27371,7 +27371,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>13693230356</t>
+          <t>136****0356</t>
         </is>
       </c>
       <c r="E477" t="n">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>18500780039</t>
+          <t>185****0039</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -27423,7 +27423,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>15055641059</t>
+          <t>150****1059</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>18627131818</t>
+          <t>186****1818</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>18385781992</t>
+          <t>183****1992</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -27501,7 +27501,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>15531182175</t>
+          <t>155****2175</t>
         </is>
       </c>
       <c r="E482" t="n">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>15011528215</t>
+          <t>150****8215</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -27553,7 +27553,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>13810575885</t>
+          <t>138****5885</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -27579,7 +27579,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E485" t="n">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>19814911319</t>
+          <t>198****1319</t>
         </is>
       </c>
       <c r="E486" t="n">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>13520701786</t>
+          <t>135****1786</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -27657,7 +27657,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>18511946513</t>
+          <t>185****6513</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>13501280368</t>
+          <t>135****0368</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>18339470337</t>
+          <t>183****0337</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -27839,7 +27839,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -27865,7 +27865,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>18633329155</t>
+          <t>186****9155</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>15902810226</t>
+          <t>159****0226</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>13811732133</t>
+          <t>138****2133</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -27995,7 +27995,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E501" t="n">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>17368461289</t>
+          <t>173****1289</t>
         </is>
       </c>
       <c r="E502" t="n">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>17634516106</t>
+          <t>176****6106</t>
         </is>
       </c>
       <c r="E503" t="n">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E504" t="n">
@@ -28099,7 +28099,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>17621765589</t>
+          <t>176****5589</t>
         </is>
       </c>
       <c r="E505" t="n">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E506" t="n">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E507" t="n">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>15811504668</t>
+          <t>158****4668</t>
         </is>
       </c>
       <c r="E508" t="n">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>18101894558</t>
+          <t>181****4558</t>
         </is>
       </c>
       <c r="E509" t="n">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>13701969018</t>
+          <t>137****9018</t>
         </is>
       </c>
       <c r="E510" t="n">
@@ -28255,7 +28255,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>18621576622</t>
+          <t>186****6622</t>
         </is>
       </c>
       <c r="E511" t="n">
@@ -28281,7 +28281,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E512" t="n">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>17301121619</t>
+          <t>173****1619</t>
         </is>
       </c>
       <c r="E513" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E514" t="n">
@@ -28359,7 +28359,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>13910824041</t>
+          <t>139****4041</t>
         </is>
       </c>
       <c r="E515" t="n">
@@ -28385,7 +28385,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>13520426123</t>
+          <t>135****6123</t>
         </is>
       </c>
       <c r="E516" t="n">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E517" t="n">
@@ -28437,7 +28437,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>18618323301</t>
+          <t>186****3301</t>
         </is>
       </c>
       <c r="E518" t="n">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E519" t="n">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>17759588798</t>
+          <t>177****8798</t>
         </is>
       </c>
       <c r="E520" t="n">
@@ -28515,7 +28515,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E521" t="n">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E522" t="n">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>13818538850</t>
+          <t>138****8850</t>
         </is>
       </c>
       <c r="E523" t="n">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>18721970468</t>
+          <t>187****0468</t>
         </is>
       </c>
       <c r="E524" t="n">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E525" t="n">
@@ -28645,7 +28645,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E526" t="n">
@@ -28671,7 +28671,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>13811276310</t>
+          <t>138****6310</t>
         </is>
       </c>
       <c r="E527" t="n">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E528" t="n">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>17702295481</t>
+          <t>177****5481</t>
         </is>
       </c>
       <c r="E529" t="n">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>18611722515</t>
+          <t>186****2515</t>
         </is>
       </c>
       <c r="E530" t="n">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E531" t="n">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E532" t="n">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E533" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E534" t="n">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="E535" t="n">
@@ -28905,7 +28905,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E536" t="n">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E537" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E538" t="n">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>13261316998</t>
+          <t>132****6998</t>
         </is>
       </c>
       <c r="E539" t="n">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>13385309523</t>
+          <t>133****9523</t>
         </is>
       </c>
       <c r="E540" t="n">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>17310230575</t>
+          <t>173****0575</t>
         </is>
       </c>
       <c r="E541" t="n">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>15530315870</t>
+          <t>155****5870</t>
         </is>
       </c>
       <c r="E542" t="n">
@@ -29087,7 +29087,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>15810955032</t>
+          <t>158****5032</t>
         </is>
       </c>
       <c r="E543" t="n">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>18612798646</t>
+          <t>186****8646</t>
         </is>
       </c>
       <c r="E544" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>17306918759</t>
+          <t>173****8759</t>
         </is>
       </c>
       <c r="E545" t="n">
@@ -29165,7 +29165,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E546" t="n">
@@ -29191,7 +29191,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="E547" t="n">
@@ -29217,7 +29217,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E548" t="n">
@@ -29243,7 +29243,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>15048686819</t>
+          <t>150****6819</t>
         </is>
       </c>
       <c r="E549" t="n">
@@ -29269,7 +29269,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>18910373510</t>
+          <t>189****3510</t>
         </is>
       </c>
       <c r="E550" t="n">
@@ -29295,7 +29295,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E551" t="n">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>18310997088</t>
+          <t>183****7088</t>
         </is>
       </c>
       <c r="E552" t="n">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E553" t="n">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E554" t="n">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>18111968858</t>
+          <t>181****8858</t>
         </is>
       </c>
       <c r="E555" t="n">
@@ -29425,7 +29425,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E556" t="n">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E557" t="n">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>13166300779</t>
+          <t>131****0779</t>
         </is>
       </c>
       <c r="E558" t="n">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E559" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E560" t="n">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E561" t="n">
@@ -29581,7 +29581,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E562" t="n">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E563" t="n">
@@ -29633,7 +29633,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E564" t="n">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>13122359792</t>
+          <t>131****9792</t>
         </is>
       </c>
       <c r="E565" t="n">
@@ -29685,7 +29685,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>15300636118</t>
+          <t>153****6118</t>
         </is>
       </c>
       <c r="E566" t="n">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E567" t="n">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>13162909498</t>
+          <t>131****9498</t>
         </is>
       </c>
       <c r="E568" t="n">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E569" t="n">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E570" t="n">
@@ -29815,7 +29815,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E571" t="n">
@@ -29841,7 +29841,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>15184398777</t>
+          <t>151****8777</t>
         </is>
       </c>
       <c r="E572" t="n">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E573" t="n">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>13959152114</t>
+          <t>139****2114</t>
         </is>
       </c>
       <c r="E574" t="n">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E575" t="n">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E576" t="n">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E577" t="n">
@@ -29997,7 +29997,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>13671927686</t>
+          <t>136****7686</t>
         </is>
       </c>
       <c r="E578" t="n">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E579" t="n">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E580" t="n">
@@ -30075,7 +30075,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E581" t="n">
@@ -30101,7 +30101,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -30127,7 +30127,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E583" t="n">
@@ -30153,7 +30153,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E584" t="n">
@@ -30179,7 +30179,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E585" t="n">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E586" t="n">
@@ -30264,7 +30264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -30292,7 +30292,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -30320,7 +30320,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -30348,7 +30348,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18210182706</t>
+          <t>182****2706</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -30376,7 +30376,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -30404,7 +30404,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -30432,7 +30432,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="B8" t="n">
